--- a/source/xlsx/A2/unit-1/Deutsch_Heimkehr_A2_U1_L1_v1.0.xlsx
+++ b/source/xlsx/A2/unit-1/Deutsch_Heimkehr_A2_U1_L1_v1.0.xlsx
@@ -1698,32 +1698,13 @@
           <t>Sofia and Lukas are sitting in a neighborhood café looking at apartment advertisements online.</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n"/>
-      <c r="B8" s="3" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n"/>
-      <c r="B12" s="3" t="n"/>
-    </row>
+    </row>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="3" t="n"/>
       <c r="B13" s="3" t="n"/>
@@ -1754,32 +1735,13 @@
 Lukas: Gern geschehen!</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n"/>
-      <c r="B16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n"/>
-      <c r="B18" s="3" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n"/>
-      <c r="B20" s="3" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n"/>
-      <c r="B21" s="3" t="n"/>
-    </row>
+    </row>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="3" t="n"/>
       <c r="B22" s="3" t="n"/>
@@ -1803,32 +1765,13 @@
 Gern geschehen! – You're welcome!</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n"/>
-      <c r="B25" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n"/>
-      <c r="B26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n"/>
-      <c r="B27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n"/>
-      <c r="B28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n"/>
-      <c r="B29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n"/>
-      <c r="B30" s="3" t="n"/>
-    </row>
+    </row>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="3" t="n"/>
       <c r="B31" s="3" t="n"/>
@@ -1854,32 +1797,13 @@
 • Public transportation</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n"/>
-      <c r="B34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n"/>
-      <c r="B35" s="3" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n"/>
-      <c r="B36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n"/>
-      <c r="B37" s="3" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="n"/>
-      <c r="B38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n"/>
-      <c r="B39" s="3" t="n"/>
-    </row>
+    </row>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="3" t="n"/>
       <c r="B40" s="3" t="n"/>
@@ -1902,32 +1826,13 @@
 • Wie hoch darf die Miete sein?</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n"/>
-      <c r="B43" s="3" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n"/>
-      <c r="B44" s="3" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n"/>
-      <c r="B45" s="3" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="n"/>
-      <c r="B46" s="3" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n"/>
-      <c r="B47" s="3" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="n"/>
-      <c r="B48" s="3" t="n"/>
-    </row>
+    </row>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A42:B48"/>
@@ -1946,9 +1851,349 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Deutsch Heimkehr A2</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Unit 1 – Finding a Home</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Lesson 1 – Questions</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Vocabulary Review</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>1. What does 'die Kaution' mean?
+2. What is the difference between Warmmiete and Kaltmiete?
+3. Translate: der Balkon, ruhig, möbliert.</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n"/>
+      <c r="B10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Grammar Practice</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Complete the sentences:
+1. Ich _______ eine Wohnung.
+2. Ich _______ einen Balkon.
+3. Die Wohnung ist _______.
+4. Ich brauche _______ Zimmer.
+5. Ich hätte gern eine _______ Wohnung.</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n"/>
+      <c r="B18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n"/>
+      <c r="B20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Reading Comprehension</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>1. How many rooms does the apartment have?
+2. How much is the Warmmiete?
+3. Is the apartment near public transportation?
+4. Are pets allowed?
+5. Why does Sofia like the apartment?</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n"/>
+      <c r="B24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n"/>
+      <c r="B26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n"/>
+      <c r="B28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Dialogue Review</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Answer in German:
+1. Was ist Sofia wichtig?
+2. Wie viele Zimmer braucht sie?
+3. Was empfiehlt Lukas?</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n"/>
+      <c r="B32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n"/>
+      <c r="B34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n"/>
+      <c r="B35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n"/>
+      <c r="B36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Real-Life Task</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Write a short message (4–6 sentences) to a landlord introducing yourself and explaining what kind of apartment you are looking for.</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n"/>
+      <c r="B39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n"/>
+      <c r="B40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n"/>
+      <c r="B41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n"/>
+      <c r="B42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n"/>
+      <c r="B43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n"/>
+      <c r="B44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Speaking Challenge</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Work with a partner.
+Student A is looking for an apartment.
+Student B is a landlord.
+Ask and answer questions about rent, rooms, location, and apartment features.</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n"/>
+      <c r="B47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n"/>
+      <c r="B48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n"/>
+      <c r="B49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n"/>
+      <c r="B50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n"/>
+      <c r="B51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n"/>
+      <c r="B52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Lesson Reflection</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>After this lesson, I can:
+□ Understand apartment advertisements.
+□ Describe an apartment.
+□ Talk about what I am looking for.
+□ Recognize common rental terms.
+□ Compare different apartments.</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n"/>
+      <c r="B55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n"/>
+      <c r="B56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n"/>
+      <c r="B57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n"/>
+      <c r="B58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n"/>
+      <c r="B59" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A46:B51"/>
+    <mergeCell ref="A38:B43"/>
+    <mergeCell ref="A54:B59"/>
+    <mergeCell ref="A6:B11"/>
+    <mergeCell ref="A14:B19"/>
+    <mergeCell ref="A30:B35"/>
+    <mergeCell ref="A22:B27"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>